--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/84.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/84.xlsx
@@ -426,13 +426,13 @@
         <v>-6.656081383887646</v>
       </c>
       <c r="E2">
-        <v>-13.91698085266427</v>
+        <v>-12.79899571812462</v>
       </c>
       <c r="F2">
-        <v>-0.8188885418567786</v>
+        <v>-1.485938019900303</v>
       </c>
       <c r="G2">
-        <v>-12.46788312211848</v>
+        <v>-9.770536690904342</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.046628170598333</v>
       </c>
       <c r="E3">
-        <v>-13.92401357279818</v>
+        <v>-14.3744291830231</v>
       </c>
       <c r="F3">
-        <v>-0.9450704348556161</v>
+        <v>-1.602039509974473</v>
       </c>
       <c r="G3">
-        <v>-11.88628979232486</v>
+        <v>-10.74683643370865</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.421197705465711</v>
       </c>
       <c r="E4">
-        <v>-14.05501779736607</v>
+        <v>-15.29780767555712</v>
       </c>
       <c r="F4">
-        <v>-0.8655819556177812</v>
+        <v>-1.383017511939478</v>
       </c>
       <c r="G4">
-        <v>-11.44342156280886</v>
+        <v>-9.760343521188926</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.836266528479246</v>
       </c>
       <c r="E5">
-        <v>-14.66995286828966</v>
+        <v>-15.47741601164934</v>
       </c>
       <c r="F5">
-        <v>-0.5701612887573935</v>
+        <v>-1.480899060989074</v>
       </c>
       <c r="G5">
-        <v>-11.22476002994</v>
+        <v>-10.52471207020571</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.275722929535052</v>
       </c>
       <c r="E6">
-        <v>-14.64690293559061</v>
+        <v>-16.32441726157</v>
       </c>
       <c r="F6">
-        <v>-0.5750685372515777</v>
+        <v>-1.439494773094946</v>
       </c>
       <c r="G6">
-        <v>-10.26778063090287</v>
+        <v>-9.415520408363978</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.748734905085813</v>
       </c>
       <c r="E7">
-        <v>-16.47924125941824</v>
+        <v>-16.65257313053583</v>
       </c>
       <c r="F7">
-        <v>-0.5918139842991698</v>
+        <v>-1.269602417352587</v>
       </c>
       <c r="G7">
-        <v>-9.698118507232785</v>
+        <v>-9.362548369190099</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.24579301822336</v>
       </c>
       <c r="E8">
-        <v>-16.53558453302167</v>
+        <v>-17.51905587563748</v>
       </c>
       <c r="F8">
-        <v>-0.2991791170143968</v>
+        <v>-0.9352609080716644</v>
       </c>
       <c r="G8">
-        <v>-9.310566183132464</v>
+        <v>-9.128363688287594</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.77643396172349</v>
       </c>
       <c r="E9">
-        <v>-17.94617248709294</v>
+        <v>-18.48988371882388</v>
       </c>
       <c r="F9">
-        <v>-0.3218415924201857</v>
+        <v>-0.836351355075195</v>
       </c>
       <c r="G9">
-        <v>-9.688650346990469</v>
+        <v>-8.456220316903826</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-2.334261505245597</v>
       </c>
       <c r="E10">
-        <v>-17.8813292677771</v>
+        <v>-18.59083246140287</v>
       </c>
       <c r="F10">
-        <v>-0.2795078763001169</v>
+        <v>-1.127303808164882</v>
       </c>
       <c r="G10">
-        <v>-9.022714248492834</v>
+        <v>-8.13074403221038</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.923614552031042</v>
       </c>
       <c r="E11">
-        <v>-19.55870773953626</v>
+        <v>-19.37551285202996</v>
       </c>
       <c r="F11">
-        <v>-0.02418930377665612</v>
+        <v>-0.9293471931830787</v>
       </c>
       <c r="G11">
-        <v>-7.680168852678953</v>
+        <v>-7.884204395355315</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-1.547987928328903</v>
       </c>
       <c r="E12">
-        <v>-19.2631251841076</v>
+        <v>-19.17587960387582</v>
       </c>
       <c r="F12">
-        <v>0.2632831778538703</v>
+        <v>-0.7227382806790345</v>
       </c>
       <c r="G12">
-        <v>-7.265049615873122</v>
+        <v>-7.208829931525218</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.208812552372184</v>
       </c>
       <c r="E13">
-        <v>-19.73523218482926</v>
+        <v>-20.82918017933619</v>
       </c>
       <c r="F13">
-        <v>0.2703905701698901</v>
+        <v>-0.3315790512400938</v>
       </c>
       <c r="G13">
-        <v>-6.855796665762878</v>
+        <v>-6.92115345579917</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-0.9207109122668693</v>
       </c>
       <c r="E14">
-        <v>-20.73605663984246</v>
+        <v>-21.12310078480404</v>
       </c>
       <c r="F14">
-        <v>0.1879158264449629</v>
+        <v>-0.3026996784762947</v>
       </c>
       <c r="G14">
-        <v>-6.603874081860958</v>
+        <v>-5.954854871068999</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.6914536350790682</v>
       </c>
       <c r="E15">
-        <v>-21.30470617793364</v>
+        <v>-22.25806769687245</v>
       </c>
       <c r="F15">
-        <v>0.6389519368604601</v>
+        <v>-0.2172419837338865</v>
       </c>
       <c r="G15">
-        <v>-5.986867846433752</v>
+        <v>-6.47518324511287</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.531638277247768</v>
       </c>
       <c r="E16">
-        <v>-22.07458751550367</v>
+        <v>-22.15606381984968</v>
       </c>
       <c r="F16">
-        <v>0.6059638617787754</v>
+        <v>-0.08132760211955761</v>
       </c>
       <c r="G16">
-        <v>-5.764803072750519</v>
+        <v>-5.147267150037029</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.4480463912878941</v>
       </c>
       <c r="E17">
-        <v>-23.97749304979283</v>
+        <v>-23.43492752198582</v>
       </c>
       <c r="F17">
-        <v>0.9538674021783313</v>
+        <v>0.1892022810215105</v>
       </c>
       <c r="G17">
-        <v>-5.552660004048482</v>
+        <v>-5.033827996588363</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.4347880973623556</v>
       </c>
       <c r="E18">
-        <v>-23.16401156447694</v>
+        <v>-23.77050103137622</v>
       </c>
       <c r="F18">
-        <v>0.7173651952094613</v>
+        <v>1.028702113347239</v>
       </c>
       <c r="G18">
-        <v>-5.320451718832922</v>
+        <v>-4.385874781460049</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.4842923014491615</v>
       </c>
       <c r="E19">
-        <v>-23.86793567812526</v>
+        <v>-25.00492228960109</v>
       </c>
       <c r="F19">
-        <v>1.398240125205709</v>
+        <v>0.8512012030101662</v>
       </c>
       <c r="G19">
-        <v>-4.771407672781414</v>
+        <v>-4.305319276852963</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.5777597091621641</v>
       </c>
       <c r="E20">
-        <v>-24.53140693346305</v>
+        <v>-25.59797577411961</v>
       </c>
       <c r="F20">
-        <v>1.832425585913459</v>
+        <v>1.159290920928969</v>
       </c>
       <c r="G20">
-        <v>-4.510079829002425</v>
+        <v>-4.284224480676727</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.6936032327760676</v>
       </c>
       <c r="E21">
-        <v>-25.31022747872422</v>
+        <v>-26.18296857490447</v>
       </c>
       <c r="F21">
-        <v>1.497698885790235</v>
+        <v>1.479797866215737</v>
       </c>
       <c r="G21">
-        <v>-4.413226508705507</v>
+        <v>-3.881228461635706</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.810905391663808</v>
       </c>
       <c r="E22">
-        <v>-25.76120009125208</v>
+        <v>-27.12682935537519</v>
       </c>
       <c r="F22">
-        <v>1.792688801601167</v>
+        <v>1.464042318214491</v>
       </c>
       <c r="G22">
-        <v>-4.106100577936241</v>
+        <v>-3.983150227153248</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.9087003682193024</v>
       </c>
       <c r="E23">
-        <v>-26.20835067171747</v>
+        <v>-27.4204918378246</v>
       </c>
       <c r="F23">
-        <v>1.849380609913959</v>
+        <v>1.190566760589068</v>
       </c>
       <c r="G23">
-        <v>-4.534955268184508</v>
+        <v>-3.138567159719922</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.9748690735452176</v>
       </c>
       <c r="E24">
-        <v>-26.70685867590384</v>
+        <v>-27.20716448427126</v>
       </c>
       <c r="F24">
-        <v>2.327227659688465</v>
+        <v>1.846371979506992</v>
       </c>
       <c r="G24">
-        <v>-4.629014488046281</v>
+        <v>-2.83918790551255</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.003700185523474</v>
       </c>
       <c r="E25">
-        <v>-26.4740452986955</v>
+        <v>-28.42145214705803</v>
       </c>
       <c r="F25">
-        <v>2.141648510439292</v>
+        <v>1.849778226267303</v>
       </c>
       <c r="G25">
-        <v>-4.282913504643176</v>
+        <v>-3.101594987137342</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.9967534599775101</v>
       </c>
       <c r="E26">
-        <v>-27.23248318244815</v>
+        <v>-27.60052132199953</v>
       </c>
       <c r="F26">
-        <v>2.586372461245457</v>
+        <v>1.823035213035324</v>
       </c>
       <c r="G26">
-        <v>-4.353894911550689</v>
+        <v>-3.833679096055154</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.9639271543013403</v>
       </c>
       <c r="E27">
-        <v>-27.43859214843325</v>
+        <v>-27.10785504928305</v>
       </c>
       <c r="F27">
-        <v>2.404746281242443</v>
+        <v>1.665517837923387</v>
       </c>
       <c r="G27">
-        <v>-4.616517178635533</v>
+        <v>-3.153795669200569</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.9168465538287111</v>
       </c>
       <c r="E28">
-        <v>-26.8780485788158</v>
+        <v>-28.91380595506798</v>
       </c>
       <c r="F28">
-        <v>2.685728504272035</v>
+        <v>2.08923273465975</v>
       </c>
       <c r="G28">
-        <v>-4.550468484581534</v>
+        <v>-4.433225514308244</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.870420718826731</v>
       </c>
       <c r="E29">
-        <v>-26.83678965213192</v>
+        <v>-28.36013208052017</v>
       </c>
       <c r="F29">
-        <v>2.599094527817652</v>
+        <v>1.901118781158011</v>
       </c>
       <c r="G29">
-        <v>-4.924954085438351</v>
+        <v>-4.026220424619166</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.8400701939861718</v>
       </c>
       <c r="E30">
-        <v>-26.75859649144148</v>
+        <v>-28.39236123003275</v>
       </c>
       <c r="F30">
-        <v>2.656006681859589</v>
+        <v>1.955254247665764</v>
       </c>
       <c r="G30">
-        <v>-4.288395768056208</v>
+        <v>-4.04791442953801</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.837623652675317</v>
       </c>
       <c r="E31">
-        <v>-26.49709975986855</v>
+        <v>-26.75558958470038</v>
       </c>
       <c r="F31">
-        <v>2.489050888560155</v>
+        <v>2.19756662359787</v>
       </c>
       <c r="G31">
-        <v>-4.879112961356062</v>
+        <v>-4.529218092764951</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.8777775397711024</v>
       </c>
       <c r="E32">
-        <v>-26.58189996413619</v>
+        <v>-27.29908797815296</v>
       </c>
       <c r="F32">
-        <v>2.130033142717237</v>
+        <v>1.886559395686407</v>
       </c>
       <c r="G32">
-        <v>-4.21184933409718</v>
+        <v>-4.636867102065433</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.9685212410158172</v>
       </c>
       <c r="E33">
-        <v>-26.34048248631327</v>
+        <v>-26.88296197311413</v>
       </c>
       <c r="F33">
-        <v>1.999233929815196</v>
+        <v>1.848300418820709</v>
       </c>
       <c r="G33">
-        <v>-4.416417874605365</v>
+        <v>-4.811743359631894</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.115664887931737</v>
       </c>
       <c r="E34">
-        <v>-25.22050029473624</v>
+        <v>-27.00501793304286</v>
       </c>
       <c r="F34">
-        <v>2.398714109815257</v>
+        <v>1.732880675119042</v>
       </c>
       <c r="G34">
-        <v>-4.68566785385983</v>
+        <v>-5.1506703908514</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.320943484557557</v>
       </c>
       <c r="E35">
-        <v>-24.70333497763826</v>
+        <v>-26.25203686046946</v>
       </c>
       <c r="F35">
-        <v>2.591061020745302</v>
+        <v>1.677504314241896</v>
       </c>
       <c r="G35">
-        <v>-5.870902746738621</v>
+        <v>-4.198458177390828</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.575739753807526</v>
       </c>
       <c r="E36">
-        <v>-25.44165737984883</v>
+        <v>-25.84868115213225</v>
       </c>
       <c r="F36">
-        <v>2.513003960379505</v>
+        <v>1.830909673566336</v>
       </c>
       <c r="G36">
-        <v>-5.55130930146846</v>
+        <v>-5.258163804511535</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.871669338399172</v>
       </c>
       <c r="E37">
-        <v>-24.71093828549714</v>
+        <v>-24.7890816329735</v>
       </c>
       <c r="F37">
-        <v>2.50590982194193</v>
+        <v>2.093903070076734</v>
       </c>
       <c r="G37">
-        <v>-5.294516905078272</v>
+        <v>-5.171586417568515</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.190739201793459</v>
       </c>
       <c r="E38">
-        <v>-23.35962352771227</v>
+        <v>-23.94885498016832</v>
       </c>
       <c r="F38">
-        <v>2.864137305282576</v>
+        <v>1.881125305524042</v>
       </c>
       <c r="G38">
-        <v>-5.337418264721688</v>
+        <v>-4.500376620026821</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.513624898526464</v>
       </c>
       <c r="E39">
-        <v>-24.11193438613254</v>
+        <v>-24.905092080102</v>
       </c>
       <c r="F39">
-        <v>2.240875328151034</v>
+        <v>2.01102988163106</v>
       </c>
       <c r="G39">
-        <v>-4.575036043028465</v>
+        <v>-4.141612799936003</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.821162290661207</v>
       </c>
       <c r="E40">
-        <v>-22.20546947127336</v>
+        <v>-23.98818930539894</v>
       </c>
       <c r="F40">
-        <v>2.664215802821332</v>
+        <v>1.911236460615804</v>
       </c>
       <c r="G40">
-        <v>-5.780551337880832</v>
+        <v>-5.33926885967814</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.090776378698409</v>
       </c>
       <c r="E41">
-        <v>-22.22197575903132</v>
+        <v>-23.75072065691072</v>
       </c>
       <c r="F41">
-        <v>2.458446026496324</v>
+        <v>1.854634115982514</v>
       </c>
       <c r="G41">
-        <v>-4.907633311176884</v>
+        <v>-4.855588224754002</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.30794831861577</v>
       </c>
       <c r="E42">
-        <v>-21.34461561936324</v>
+        <v>-22.9592384983241</v>
       </c>
       <c r="F42">
-        <v>2.057713354983229</v>
+        <v>1.852220253370756</v>
       </c>
       <c r="G42">
-        <v>-5.004738232934787</v>
+        <v>-5.232586529675126</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.459116416931269</v>
       </c>
       <c r="E43">
-        <v>-21.51842750872564</v>
+        <v>-21.35142191579677</v>
       </c>
       <c r="F43">
-        <v>2.660098816829419</v>
+        <v>1.983188453222969</v>
       </c>
       <c r="G43">
-        <v>-5.259355600905673</v>
+        <v>-3.859660257447354</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.537416696828529</v>
       </c>
       <c r="E44">
-        <v>-20.61977901274751</v>
+        <v>-22.18575249544396</v>
       </c>
       <c r="F44">
-        <v>2.342819190943958</v>
+        <v>1.938655421648468</v>
       </c>
       <c r="G44">
-        <v>-5.139368188380327</v>
+        <v>-5.070330071704366</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.544789150780687</v>
       </c>
       <c r="E45">
-        <v>-20.31328283496036</v>
+        <v>-20.88252560314655</v>
       </c>
       <c r="F45">
-        <v>2.320575869443985</v>
+        <v>1.75524990846424</v>
       </c>
       <c r="G45">
-        <v>-4.681834242125354</v>
+        <v>-4.373311261138515</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.485650407472004</v>
       </c>
       <c r="E46">
-        <v>-21.06401325595196</v>
+        <v>-21.32385256603807</v>
       </c>
       <c r="F46">
-        <v>2.408114423102226</v>
+        <v>1.781162897558614</v>
       </c>
       <c r="G46">
-        <v>-4.72245794643775</v>
+        <v>-3.393568550973364</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.376569235434036</v>
       </c>
       <c r="E47">
-        <v>-20.46383195334537</v>
+        <v>-21.25395104125567</v>
       </c>
       <c r="F47">
-        <v>1.971896148788006</v>
+        <v>1.556282685251021</v>
       </c>
       <c r="G47">
-        <v>-4.64623594594157</v>
+        <v>-4.688120968104429</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.234716192045617</v>
       </c>
       <c r="E48">
-        <v>-19.165948660377</v>
+        <v>-19.99786556337811</v>
       </c>
       <c r="F48">
-        <v>2.047958500447862</v>
+        <v>1.630635286591499</v>
       </c>
       <c r="G48">
-        <v>-4.654889711981225</v>
+        <v>-4.298214846125687</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.081791939672408</v>
       </c>
       <c r="E49">
-        <v>-18.46957804137348</v>
+        <v>-19.83579147864359</v>
       </c>
       <c r="F49">
-        <v>2.083487178353933</v>
+        <v>1.654462446565624</v>
       </c>
       <c r="G49">
-        <v>-4.811458652715517</v>
+        <v>-4.324424435160097</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.943681271067309</v>
       </c>
       <c r="E50">
-        <v>-18.17130557238427</v>
+        <v>-19.22732306860296</v>
       </c>
       <c r="F50">
-        <v>2.368811703309</v>
+        <v>1.587127773861664</v>
       </c>
       <c r="G50">
-        <v>-5.829034277303458</v>
+        <v>-4.084522442111271</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.837533230938984</v>
       </c>
       <c r="E51">
-        <v>-17.20967053143345</v>
+        <v>-18.45231549845624</v>
       </c>
       <c r="F51">
-        <v>1.879193552740714</v>
+        <v>1.692855618950576</v>
       </c>
       <c r="G51">
-        <v>-5.119481741325925</v>
+        <v>-4.346863312825277</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.786059067936559</v>
       </c>
       <c r="E52">
-        <v>-17.03767908862212</v>
+        <v>-18.04203575336131</v>
       </c>
       <c r="F52">
-        <v>1.88266938236286</v>
+        <v>1.400518135563408</v>
       </c>
       <c r="G52">
-        <v>-5.532687482810059</v>
+        <v>-4.599401658197501</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.800002024929201</v>
       </c>
       <c r="E53">
-        <v>-16.81322074595793</v>
+        <v>-18.06856355409824</v>
       </c>
       <c r="F53">
-        <v>1.911566150842118</v>
+        <v>1.646243385195048</v>
       </c>
       <c r="G53">
-        <v>-4.554312027952627</v>
+        <v>-3.506722997505653</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.885295244537418</v>
       </c>
       <c r="E54">
-        <v>-15.73625905745377</v>
+        <v>-17.3576565335301</v>
       </c>
       <c r="F54">
-        <v>2.042767950301921</v>
+        <v>1.591418717008165</v>
       </c>
       <c r="G54">
-        <v>-4.744102293173505</v>
+        <v>-4.578853102035245</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.04617914439868</v>
       </c>
       <c r="E55">
-        <v>-16.45380029244315</v>
+        <v>-17.52778677352427</v>
       </c>
       <c r="F55">
-        <v>1.817084221613612</v>
+        <v>1.448921299643789</v>
       </c>
       <c r="G55">
-        <v>-5.108196091582551</v>
+        <v>-4.451373924954529</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.270805351097438</v>
       </c>
       <c r="E56">
-        <v>-16.50827783475542</v>
+        <v>-16.58211460345049</v>
       </c>
       <c r="F56">
-        <v>1.700718482337949</v>
+        <v>1.43116772946699</v>
       </c>
       <c r="G56">
-        <v>-6.496920287123724</v>
+        <v>-4.891957878048435</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.554583381109016</v>
       </c>
       <c r="E57">
-        <v>-15.31305051906694</v>
+        <v>-15.8955028459335</v>
       </c>
       <c r="F57">
-        <v>1.692073640122333</v>
+        <v>1.107339030894996</v>
       </c>
       <c r="G57">
-        <v>-5.565696932382132</v>
+        <v>-5.017996967819568</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.88275022140727</v>
       </c>
       <c r="E58">
-        <v>-15.037375135376</v>
+        <v>-14.65742258071043</v>
       </c>
       <c r="F58">
-        <v>1.73503111689671</v>
+        <v>1.039772415318251</v>
       </c>
       <c r="G58">
-        <v>-5.58083274658768</v>
+        <v>-4.54326142694254</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.238699433139537</v>
       </c>
       <c r="E59">
-        <v>-14.99385650016229</v>
+        <v>-14.52284539015048</v>
       </c>
       <c r="F59">
-        <v>1.674161023404197</v>
+        <v>1.567397719061785</v>
       </c>
       <c r="G59">
-        <v>-6.182305902344626</v>
+        <v>-5.105061004956861</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.612998457439153</v>
       </c>
       <c r="E60">
-        <v>-14.31780061555718</v>
+        <v>-14.93536672987921</v>
       </c>
       <c r="F60">
-        <v>2.30067517095913</v>
+        <v>1.59600952915448</v>
       </c>
       <c r="G60">
-        <v>-5.684714355064471</v>
+        <v>-5.146912921664327</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.985681633008616</v>
       </c>
       <c r="E61">
-        <v>-15.68369705964674</v>
+        <v>-14.81872229638964</v>
       </c>
       <c r="F61">
-        <v>1.848330240047209</v>
+        <v>1.274798471575333</v>
       </c>
       <c r="G61">
-        <v>-5.909315006630785</v>
+        <v>-5.5836500208416</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.349646411750615</v>
       </c>
       <c r="E62">
-        <v>-15.40917190835375</v>
+        <v>-14.61624063808468</v>
       </c>
       <c r="F62">
-        <v>1.477945636703078</v>
+        <v>1.408382655685587</v>
       </c>
       <c r="G62">
-        <v>-6.17865768116035</v>
+        <v>-5.488137471488087</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.693857090913276</v>
       </c>
       <c r="E63">
-        <v>-13.88463396282748</v>
+        <v>-15.90495377118751</v>
       </c>
       <c r="F63">
-        <v>1.740483431141936</v>
+        <v>1.741954611649308</v>
       </c>
       <c r="G63">
-        <v>-6.343254694827373</v>
+        <v>-6.117693985054671</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.0064813538804</v>
       </c>
       <c r="E64">
-        <v>-13.83775519990007</v>
+        <v>-13.87211273219627</v>
       </c>
       <c r="F64">
-        <v>1.747933767562715</v>
+        <v>0.9333106367104589</v>
       </c>
       <c r="G64">
-        <v>-6.821876816167506</v>
+        <v>-6.613160162098614</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.285850548161276</v>
       </c>
       <c r="E65">
-        <v>-13.45166656295411</v>
+        <v>-14.38153435874113</v>
       </c>
       <c r="F65">
-        <v>1.33740979334853</v>
+        <v>1.364735977232081</v>
       </c>
       <c r="G65">
-        <v>-6.562829938265074</v>
+        <v>-5.77256961258565</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.520518208448051</v>
       </c>
       <c r="E66">
-        <v>-13.2588350827595</v>
+        <v>-13.93581930453618</v>
       </c>
       <c r="F66">
-        <v>1.348871084733664</v>
+        <v>0.8157006895957907</v>
       </c>
       <c r="G66">
-        <v>-6.418519947662704</v>
+        <v>-5.873114191158854</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.710783781578862</v>
       </c>
       <c r="E67">
-        <v>-13.65611810745242</v>
+        <v>-14.33229173238172</v>
       </c>
       <c r="F67">
-        <v>1.782002862105053</v>
+        <v>0.9523084147262627</v>
       </c>
       <c r="G67">
-        <v>-6.431000704345757</v>
+        <v>-5.654085187735133</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.853569754705574</v>
       </c>
       <c r="E68">
-        <v>-12.99789535348951</v>
+        <v>-14.5496584847499</v>
       </c>
       <c r="F68">
-        <v>1.540621571133694</v>
+        <v>0.9213307873311724</v>
       </c>
       <c r="G68">
-        <v>-6.494990239074329</v>
+        <v>-5.490749491918572</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.944384281458495</v>
       </c>
       <c r="E69">
-        <v>-13.47269679624574</v>
+        <v>-13.98680086491453</v>
       </c>
       <c r="F69">
-        <v>1.597271961076347</v>
+        <v>0.6271824928014847</v>
       </c>
       <c r="G69">
-        <v>-5.553739241894284</v>
+        <v>-6.065976642640176</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.988854922688798</v>
       </c>
       <c r="E70">
-        <v>-14.11142446960562</v>
+        <v>-13.5291759240694</v>
       </c>
       <c r="F70">
-        <v>1.677202788507276</v>
+        <v>0.8271669511853413</v>
       </c>
       <c r="G70">
-        <v>-5.7342765323329</v>
+        <v>-5.860077262825205</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.982799955819742</v>
       </c>
       <c r="E71">
-        <v>-13.60134168585564</v>
+        <v>-14.19345777625457</v>
       </c>
       <c r="F71">
-        <v>1.718694054978698</v>
+        <v>0.6455689356740225</v>
       </c>
       <c r="G71">
-        <v>-5.90520330907101</v>
+        <v>-5.284419741183495</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.93430619739702</v>
       </c>
       <c r="E72">
-        <v>-13.10599908500062</v>
+        <v>-15.09747251393179</v>
       </c>
       <c r="F72">
-        <v>1.507652548502274</v>
+        <v>0.8793822620534054</v>
       </c>
       <c r="G72">
-        <v>-5.436625382897027</v>
+        <v>-5.834000095612366</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.847064650241897</v>
       </c>
       <c r="E73">
-        <v>-14.45048490398192</v>
+        <v>-14.73482778692354</v>
       </c>
       <c r="F73">
-        <v>1.3080773036154</v>
+        <v>0.4048022933155406</v>
       </c>
       <c r="G73">
-        <v>-5.454330180441049</v>
+        <v>-5.85818694132228</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.723392630152373</v>
       </c>
       <c r="E74">
-        <v>-14.84012386454989</v>
+        <v>-14.82358134899987</v>
       </c>
       <c r="F74">
-        <v>1.684563661248553</v>
+        <v>0.5150381138104877</v>
       </c>
       <c r="G74">
-        <v>-5.377740709390011</v>
+        <v>-6.071922382428707</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.574144963067038</v>
       </c>
       <c r="E75">
-        <v>-14.97831477736796</v>
+        <v>-13.70047451035755</v>
       </c>
       <c r="F75">
-        <v>1.235225704008795</v>
+        <v>0.3138409255489326</v>
       </c>
       <c r="G75">
-        <v>-5.05259878979603</v>
+        <v>-5.220592423186346</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.398184437966458</v>
       </c>
       <c r="E76">
-        <v>-14.37283063169839</v>
+        <v>-14.72091178629797</v>
       </c>
       <c r="F76">
-        <v>1.193504151399395</v>
+        <v>0.3416459057913007</v>
       </c>
       <c r="G76">
-        <v>-4.798580630567752</v>
+        <v>-5.782080809919975</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.205551619519361</v>
       </c>
       <c r="E77">
-        <v>-14.34162944578554</v>
+        <v>-15.1974295207031</v>
       </c>
       <c r="F77">
-        <v>1.233696537783227</v>
+        <v>0.4482410515509439</v>
       </c>
       <c r="G77">
-        <v>-5.068105385101976</v>
+        <v>-5.20708870793166</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.998910616059122</v>
       </c>
       <c r="E78">
-        <v>-15.51457666935628</v>
+        <v>-15.86142155055177</v>
       </c>
       <c r="F78">
-        <v>1.220421121785962</v>
+        <v>0.2386533298664326</v>
       </c>
       <c r="G78">
-        <v>-4.305398729945906</v>
+        <v>-4.921365454073781</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.778721376623372</v>
       </c>
       <c r="E79">
-        <v>-16.19184165652144</v>
+        <v>-16.49059414375547</v>
       </c>
       <c r="F79">
-        <v>0.6690324423583186</v>
+        <v>0.1554661901750979</v>
       </c>
       <c r="G79">
-        <v>-3.752223123061386</v>
+        <v>-4.712403819634984</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.551782341332036</v>
       </c>
       <c r="E80">
-        <v>-17.2222189329087</v>
+        <v>-17.02344156634201</v>
       </c>
       <c r="F80">
-        <v>1.213835600933706</v>
+        <v>0.277617247391913</v>
       </c>
       <c r="G80">
-        <v>-4.49443088023829</v>
+        <v>-4.26317934268358</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.312455871748814</v>
       </c>
       <c r="E81">
-        <v>-17.08750588812852</v>
+        <v>-17.66771662036129</v>
       </c>
       <c r="F81">
-        <v>0.9315180496508007</v>
+        <v>0.3017575302442961</v>
       </c>
       <c r="G81">
-        <v>-4.380640808962461</v>
+        <v>-2.765743452723819</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.065216862675603</v>
       </c>
       <c r="E82">
-        <v>-17.90667966527204</v>
+        <v>-19.01191261700609</v>
       </c>
       <c r="F82">
-        <v>0.6814115648257544</v>
+        <v>0.1275775448250469</v>
       </c>
       <c r="G82">
-        <v>-3.725649374017657</v>
+        <v>-3.233857902522304</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.807571804094782</v>
       </c>
       <c r="E83">
-        <v>-19.00442704947142</v>
+        <v>-19.17765023721282</v>
       </c>
       <c r="F83">
-        <v>1.218408188997159</v>
+        <v>0.2314332795836321</v>
       </c>
       <c r="G83">
-        <v>-2.88842895986367</v>
+        <v>-3.695450577608425</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.536044559287614</v>
       </c>
       <c r="E84">
-        <v>-20.12915508180849</v>
+        <v>-20.67825066913455</v>
       </c>
       <c r="F84">
-        <v>0.9460840620616272</v>
+        <v>-0.06216332225579106</v>
       </c>
       <c r="G84">
-        <v>-2.828173720503395</v>
+        <v>-3.062772219598308</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.254920205621053</v>
       </c>
       <c r="E85">
-        <v>-20.98719222288583</v>
+        <v>-21.3163126568153</v>
       </c>
       <c r="F85">
-        <v>0.882061202234059</v>
+        <v>0.006495081557843172</v>
       </c>
       <c r="G85">
-        <v>-1.883843915971828</v>
+        <v>-3.06776121172599</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.960069335754437</v>
       </c>
       <c r="E86">
-        <v>-22.14700234336033</v>
+        <v>-22.66650435304626</v>
       </c>
       <c r="F86">
-        <v>1.101119648434777</v>
+        <v>0.1383148431001341</v>
       </c>
       <c r="G86">
-        <v>-2.182845767987723</v>
+        <v>-2.131479343400391</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.658950084456664</v>
       </c>
       <c r="E87">
-        <v>-23.44503960444495</v>
+        <v>-22.95691086268416</v>
       </c>
       <c r="F87">
-        <v>0.6644217493943365</v>
+        <v>0.2363728344065256</v>
       </c>
       <c r="G87">
-        <v>-2.481943625824257</v>
+        <v>-2.143913752445894</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.356855976112071</v>
       </c>
       <c r="E88">
-        <v>-24.67941557792975</v>
+        <v>-24.2516513946912</v>
       </c>
       <c r="F88">
-        <v>0.8574736009841641</v>
+        <v>0.01042899835373802</v>
       </c>
       <c r="G88">
-        <v>-2.093182952602102</v>
+        <v>-2.438691348353679</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.059049523531492</v>
       </c>
       <c r="E89">
-        <v>-25.58460771884896</v>
+        <v>-26.94556359779616</v>
       </c>
       <c r="F89">
-        <v>0.798288406788945</v>
+        <v>-0.4010003814317064</v>
       </c>
       <c r="G89">
-        <v>-2.068648499610564</v>
+        <v>-2.215057376084832</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.780912617424422</v>
       </c>
       <c r="E90">
-        <v>-27.76275843179833</v>
+        <v>-26.85934145269012</v>
       </c>
       <c r="F90">
-        <v>0.465824806410169</v>
+        <v>-0.1395477482905153</v>
       </c>
       <c r="G90">
-        <v>-1.066288142321112</v>
+        <v>-1.298267999894462</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.52965688308423</v>
       </c>
       <c r="E91">
-        <v>-29.24566158729808</v>
+        <v>-28.96918466370778</v>
       </c>
       <c r="F91">
-        <v>0.5224155538998201</v>
+        <v>-0.378550796448437</v>
       </c>
       <c r="G91">
-        <v>-1.871684282206085</v>
+        <v>-2.118670842708951</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.320178893941572</v>
       </c>
       <c r="E92">
-        <v>-30.65066593291789</v>
+        <v>-32.37133208771636</v>
       </c>
       <c r="F92">
-        <v>0.2182241329785912</v>
+        <v>0.002167690245618554</v>
       </c>
       <c r="G92">
-        <v>-1.673462057496683</v>
+        <v>-1.949995236937545</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.165384255175029</v>
       </c>
       <c r="E93">
-        <v>-32.9310990240415</v>
+        <v>-32.88464593767082</v>
       </c>
       <c r="F93">
-        <v>0.4791002224074339</v>
+        <v>-0.4399626422223812</v>
       </c>
       <c r="G93">
-        <v>-2.126242060357264</v>
+        <v>-1.995720491925959</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.070805560821628</v>
       </c>
       <c r="E94">
-        <v>-34.93601975653845</v>
+        <v>-35.54211977467306</v>
       </c>
       <c r="F94">
-        <v>0.651466911581955</v>
+        <v>-0.7154171695730924</v>
       </c>
       <c r="G94">
-        <v>-2.742576255039999</v>
+        <v>-2.105326033640149</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.047190121894053</v>
       </c>
       <c r="E95">
-        <v>-36.93626483962247</v>
+        <v>-37.33671100340975</v>
       </c>
       <c r="F95">
-        <v>0.17802014945112</v>
+        <v>-0.6992656619533076</v>
       </c>
       <c r="G95">
-        <v>-1.73711722712579</v>
+        <v>-1.675269615361126</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.097455698994534</v>
       </c>
       <c r="E96">
-        <v>-40.09718045324245</v>
+        <v>-39.44616023718875</v>
       </c>
       <c r="F96">
-        <v>-0.1052193747511009</v>
+        <v>-0.5522702095917298</v>
       </c>
       <c r="G96">
-        <v>-1.987007136066597</v>
+        <v>-3.170050447798391</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.216411499168379</v>
       </c>
       <c r="E97">
-        <v>-41.50773444375866</v>
+        <v>-41.90212150932367</v>
       </c>
       <c r="F97">
-        <v>-0.04755671984222737</v>
+        <v>-1.046757503753672</v>
       </c>
       <c r="G97">
-        <v>-2.707464609050489</v>
+        <v>-2.456316692804759</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.413193755679824</v>
       </c>
       <c r="E98">
-        <v>-44.80403105207495</v>
+        <v>-44.13240854352335</v>
       </c>
       <c r="F98">
-        <v>0.05664610085813084</v>
+        <v>-0.7478626640059434</v>
       </c>
       <c r="G98">
-        <v>-2.27884165698997</v>
+        <v>-3.326003627062378</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.66214128262097</v>
       </c>
       <c r="E99">
-        <v>-46.13293212775885</v>
+        <v>-46.55321980041073</v>
       </c>
       <c r="F99">
-        <v>-0.1879848754344108</v>
+        <v>-1.124122877338132</v>
       </c>
       <c r="G99">
-        <v>-3.024780398989632</v>
+        <v>-3.59226749424042</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.986974244623641</v>
       </c>
       <c r="E100">
-        <v>-48.71341058544568</v>
+        <v>-49.30786110419556</v>
       </c>
       <c r="F100">
-        <v>-0.6330227774862367</v>
+        <v>-1.193003283615717</v>
       </c>
       <c r="G100">
-        <v>-2.699565647393788</v>
+        <v>-3.990761171348033</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.337761748998877</v>
       </c>
       <c r="E101">
-        <v>-50.93040088784033</v>
+        <v>-50.75743355888036</v>
       </c>
       <c r="F101">
-        <v>-0.7083089488896698</v>
+        <v>-1.296783636940647</v>
       </c>
       <c r="G101">
-        <v>-3.52899303734833</v>
+        <v>-4.259153719307826</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.776892555015455</v>
       </c>
       <c r="E102">
-        <v>-52.69861715183784</v>
+        <v>-53.46651048931851</v>
       </c>
       <c r="F102">
-        <v>-1.156391929514187</v>
+        <v>-1.347330615859473</v>
       </c>
       <c r="G102">
-        <v>-3.857111137382115</v>
+        <v>-4.131422940766126</v>
       </c>
     </row>
   </sheetData>
